--- a/data/trans_dic/CAGE_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,81</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,94</t>
+          <t>5,25; 11,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,68</t>
+          <t>2,83; 8,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,07</t>
+          <t>1,27; 9,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,89</t>
+          <t>0,93; 5,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,78</t>
+          <t>0,18; 1,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,99</t>
+          <t>2,6; 6,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,42</t>
+          <t>2,25; 5,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,99</t>
+          <t>0,59; 6,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,71</t>
+          <t>0,6; 2,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,04</t>
+          <t>1,13; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,99</t>
+          <t>0,22; 2,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,28</t>
+          <t>0,29; 1,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,08</t>
+          <t>0,51; 2,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,16</t>
+          <t>0,2; 1,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,09</t>
+          <t>2,5; 8,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,93</t>
+          <t>0,49; 5,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,76</t>
+          <t>2,26; 6,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,83</t>
+          <t>0,57; 3,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,4; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,35</t>
+          <t>0,41; 2,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,79</t>
+          <t>0,35; 2,47</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,02</t>
+          <t>1,1; 5,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,66</t>
+          <t>0,44; 3,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,85</t>
+          <t>0,67; 3,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,95</t>
+          <t>1,01; 5,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,04</t>
+          <t>0,57; 6,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,24</t>
+          <t>0,31; 2,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,77</t>
+          <t>1,17; 4,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,19</t>
+          <t>0,14; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,26</t>
+          <t>0,97; 3,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,12</t>
+          <t>1,54; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,54</t>
+          <t>1,52; 5,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,99</t>
+          <t>0,31; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,66</t>
+          <t>0,16; 4,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,72</t>
+          <t>0,07; 0,61</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,71</t>
+          <t>0,59; 1,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,6</t>
+          <t>1,06; 2,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,07</t>
+          <t>0,81; 4,04</t>
         </is>
       </c>
     </row>
@@ -1702,57 +1702,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,85</t>
+          <t>0,67; 2,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,44</t>
+          <t>0,24; 1,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,24</t>
+          <t>0,37; 3,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,76</t>
+          <t>0,13; 0,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,44</t>
+          <t>0,4; 1,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,92</t>
+          <t>0,2; 0,92</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,83</t>
+          <t>0,61; 2,85</t>
         </is>
       </c>
     </row>
@@ -1837,27 +1837,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,19</t>
+          <t>0,52; 1,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,51</t>
+          <t>1,46; 2,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,94</t>
+          <t>1,06; 1,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,1</t>
+          <t>1,65; 3,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,52</t>
+          <t>0,13; 0,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1867,32 +1867,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,79</t>
+          <t>0,28; 0,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,23</t>
+          <t>0,56; 2,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,73</t>
+          <t>0,36; 0,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,79; 1,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,23</t>
+          <t>0,73; 1,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,47</t>
+          <t>1,26; 2,49</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>924; 7681</t>
+          <t>0; 7531</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14226; 32252</t>
+          <t>15479; 33886</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8770; 25504</t>
+          <t>8323; 24446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1593; 16321</t>
+          <t>2284; 16986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 4563</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4658</t>
+          <t>0; 5614</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2039; 14117</t>
+          <t>2674; 14435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>966; 9506</t>
+          <t>969; 8720</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15508; 34840</t>
+          <t>15129; 36517</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12531; 31544</t>
+          <t>13123; 32616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1649; 16204</t>
+          <t>1590; 16283</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2959; 13340</t>
+          <t>2949; 13751</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5455; 20421</t>
+          <t>5737; 21466</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1123; 10023</t>
+          <t>1119; 10913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2729</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1935</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 6715</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1510</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2845; 12788</t>
+          <t>2862; 13161</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5808; 21430</t>
+          <t>5217; 22180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2138; 11948</t>
+          <t>2087; 12125</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2202</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5168; 16826</t>
+          <t>4622; 16007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5194</t>
+          <t>0; 5592</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 4446</t>
+          <t>446; 4887</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 5997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3969</t>
+          <t>0; 4354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6070; 18625</t>
+          <t>6234; 17816</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1965; 13727</t>
+          <t>2035; 13581</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4914</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 6847</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6850</t>
+          <t>717; 6770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 8897</t>
+          <t>0; 7984</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3768; 17134</t>
+          <t>3017; 16473</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5294</t>
+          <t>0; 3716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5938</t>
+          <t>0; 7606</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1251; 8420</t>
+          <t>1048; 7461</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5389</t>
+          <t>0; 4877</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2812; 12806</t>
+          <t>2349; 12604</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>940; 7732</t>
+          <t>934; 7572</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1267</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8261</t>
+          <t>0; 8115</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1873</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 9666</t>
+          <t>0; 10236</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2317; 12314</t>
+          <t>2880; 12974</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931; 7630</t>
+          <t>934; 7655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2437</t>
+          <t>0; 2490</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9370</t>
+          <t>0; 10945</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5824</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7047</t>
+          <t>0; 6761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1939; 9813</t>
+          <t>1668; 9370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6055</t>
+          <t>0; 7224</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5361</t>
+          <t>0; 5571</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>526; 5825</t>
+          <t>552; 6135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1029; 12315</t>
+          <t>1725; 13721</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5343</t>
+          <t>0; 5300</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>902; 8541</t>
+          <t>903; 8517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3156; 12466</t>
+          <t>3066; 12094</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>850; 7325</t>
+          <t>850; 8412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5915; 21602</t>
+          <t>6445; 21634</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9723; 27049</t>
+          <t>10121; 28748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4826; 17063</t>
+          <t>4693; 16916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6621</t>
+          <t>0; 6824</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2115; 13726</t>
+          <t>2134; 12275</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>538; 18610</t>
+          <t>629; 18343</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>850; 9009</t>
+          <t>850; 7622</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7654; 23261</t>
+          <t>7949; 24468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13627; 35021</t>
+          <t>14312; 35416</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6224; 28808</t>
+          <t>5748; 28603</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>880; 8748</t>
+          <t>888; 8757</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5882; 22232</t>
+          <t>5191; 22887</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1972; 11174</t>
+          <t>1896; 12050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925; 8952</t>
+          <t>1016; 9479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6519</t>
+          <t>0; 7405</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4970</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7753</t>
+          <t>0; 7073</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5648</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2550; 11606</t>
+          <t>1953; 11573</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6065; 23115</t>
+          <t>6378; 24321</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3117; 14693</t>
+          <t>3135; 14844</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2005; 10629</t>
+          <t>2284; 10707</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17045; 38902</t>
+          <t>17014; 38046</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50279; 85946</t>
+          <t>50005; 84334</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36392; 65896</t>
+          <t>36011; 65692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24755; 48734</t>
+          <t>25905; 50138</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3720; 17659</t>
+          <t>4326; 18367</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1986; 11405</t>
+          <t>1989; 11445</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9745; 28031</t>
+          <t>9870; 27129</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5789; 22683</t>
+          <t>5657; 24072</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24809; 48344</t>
+          <t>24204; 47707</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55135; 91422</t>
+          <t>55382; 90084</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>51351; 85316</t>
+          <t>50398; 83590</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>34586; 64109</t>
+          <t>32694; 64580</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/CAGE_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/CAGE_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,34; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 11,5</t>
+          <t>5,22; 11,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,32</t>
+          <t>2,77; 8,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 9,44</t>
+          <t>0,76; 6,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,0</t>
+          <t>0,95; 5,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,63</t>
+          <t>0,18; 1,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,27</t>
+          <t>2,6; 6,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,6</t>
+          <t>2,33; 5,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,02</t>
+          <t>0,49; 4,74</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,79</t>
+          <t>0,61; 2,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,25</t>
+          <t>1,15; 4,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,17</t>
+          <t>0,22; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,32</t>
+          <t>0,3; 1,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,15</t>
+          <t>0,59; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,18</t>
+          <t>0,21; 1,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,64</t>
+          <t>3,14; 9,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,41</t>
+          <t>0,47; 4,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,47</t>
+          <t>2,79; 7,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,79</t>
+          <t>0,57; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,81</t>
+          <t>0,34; 3,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,26</t>
+          <t>0,47; 2,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,47</t>
+          <t>0,35; 2,33</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,93</t>
+          <t>1,16; 6,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,58</t>
+          <t>0,44; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,0</t>
+          <t>0,61; 3,14</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,78</t>
+          <t>0,22; 1,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,68</t>
+          <t>0,97; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,56; 6,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,5</t>
+          <t>0,19; 2,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,59</t>
+          <t>0,17; 1,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,63</t>
+          <t>1,2; 4,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,37</t>
+          <t>0,14; 1,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,26</t>
+          <t>0,89; 3,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,38</t>
+          <t>1,51; 4,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,49</t>
+          <t>2,17; 7,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,78</t>
+          <t>0,3; 1,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,59</t>
+          <t>1,66; 8,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,8</t>
+          <t>0,59; 1,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,63</t>
+          <t>1,04; 2,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,04</t>
+          <t>2,61; 6,5</t>
         </is>
       </c>
     </row>
@@ -1644,47 +1644,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,18</t>
+          <t>0,12; 1,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,94</t>
+          <t>0,78; 3,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,55</t>
+          <t>0,25; 1,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,43</t>
+          <t>0,35; 3,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,76</t>
+          <t>0,14; 0,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,52</t>
+          <t>0,37; 1,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,92</t>
+          <t>0,19; 0,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,85</t>
+          <t>0,45; 2,74</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,16</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,45; 2,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,94</t>
+          <t>1,06; 1,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,19</t>
+          <t>1,78; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,54</t>
+          <t>0,14; 0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,32</t>
+          <t>0,06; 0,34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,77</t>
+          <t>0,26; 0,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,37</t>
+          <t>1,09; 3,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,72</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,79; 1,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,2</t>
+          <t>0,74; 1,21</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,49</t>
+          <t>1,72; 2,89</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>4920</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2209,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7531</t>
+          <t>924; 7522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15479; 33886</t>
+          <t>15393; 33210</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8323; 24446</t>
+          <t>8147; 26004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2284; 16986</t>
+          <t>1291; 11829</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 4981</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5614</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2674; 14435</t>
+          <t>2730; 14667</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>969; 8720</t>
+          <t>959; 9525</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15129; 36517</t>
+          <t>15133; 35410</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13123; 32616</t>
+          <t>13558; 33481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1590; 16283</t>
+          <t>1299; 12661</t>
         </is>
       </c>
     </row>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2949; 13751</t>
+          <t>3017; 13327</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5737; 21466</t>
+          <t>5799; 21635</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1119; 10913</t>
+          <t>1111; 9865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6715</t>
+          <t>0; 6324</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,17 +2457,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2862; 13161</t>
+          <t>2956; 13475</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5217; 22180</t>
+          <t>6095; 21143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2087; 12125</t>
+          <t>2144; 12117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>12786</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3504</t>
+          <t>0; 5268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4622; 16007</t>
+          <t>5881; 18123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5592</t>
+          <t>0; 4921</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>446; 4887</t>
+          <t>419; 4401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5997</t>
+          <t>0; 3966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 4150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6234; 17816</t>
+          <t>7714; 21143</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3420</t>
         </is>
       </c>
     </row>
@@ -2833,27 +2833,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2035; 13581</t>
+          <t>2042; 13893</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5054</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6847</t>
+          <t>0; 7853</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>717; 6770</t>
+          <t>692; 7056</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7984</t>
+          <t>0; 9872</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3017; 16473</t>
+          <t>3438; 17038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3716</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 7606</t>
+          <t>0; 6368</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1048; 7461</t>
+          <t>1188; 7962</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4877</t>
+          <t>0; 4548</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2349; 12604</t>
+          <t>2475; 12753</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>934; 7572</t>
+          <t>935; 7668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8115</t>
+          <t>0; 8266</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 10236</t>
+          <t>0; 8352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2880; 12974</t>
+          <t>2640; 13571</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>934; 7655</t>
+          <t>943; 7718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2490</t>
+          <t>0; 2472</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6536</t>
         </is>
       </c>
     </row>
@@ -3249,27 +3249,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 10945</t>
+          <t>0; 11037</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 5275</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6761</t>
+          <t>0; 6663</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1668; 9370</t>
+          <t>1574; 9030</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7224</t>
+          <t>0; 7051</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5571</t>
+          <t>0; 4765</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>552; 6135</t>
+          <t>546; 6213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1725; 13721</t>
+          <t>1030; 11710</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 5297</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>903; 8517</t>
+          <t>890; 7605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3066; 12094</t>
+          <t>3130; 12080</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9216</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>24187</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>850; 8412</t>
+          <t>847; 7275</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6445; 21634</t>
+          <t>5920; 21878</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10121; 28748</t>
+          <t>9897; 28728</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4693; 16916</t>
+          <t>7586; 26140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6824</t>
+          <t>0; 6605</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2134; 12275</t>
+          <t>2092; 12318</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>629; 18343</t>
+          <t>3871; 20202</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>850; 7622</t>
+          <t>849; 7782</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7949; 24468</t>
+          <t>7981; 23784</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14312; 35416</t>
+          <t>13986; 35279</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5748; 28603</t>
+          <t>15219; 37925</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1561</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5540</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>888; 8757</t>
+          <t>881; 8973</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5191; 22887</t>
+          <t>6075; 23537</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1896; 12050</t>
+          <t>1937; 12082</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1016; 9479</t>
+          <t>1109; 9436</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 7405</t>
+          <t>0; 7127</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7073</t>
+          <t>0; 7696</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 5396</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1953; 11573</t>
+          <t>2154; 12017</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6378; 24321</t>
+          <t>5973; 23295</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3135; 14844</t>
+          <t>3065; 14346</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2284; 10707</t>
+          <t>1902; 11722</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>57858</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>17014; 38046</t>
+          <t>16852; 37973</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50005; 84334</t>
+          <t>49698; 84873</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36011; 65692</t>
+          <t>36001; 64060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25905; 50138</t>
+          <t>29825; 55525</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4326; 18367</t>
+          <t>4632; 18511</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1989; 11445</t>
+          <t>1979; 12225</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9870; 27129</t>
+          <t>9260; 26200</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5657; 24072</t>
+          <t>9748; 28483</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>24204; 47707</t>
+          <t>24974; 48973</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55382; 90084</t>
+          <t>55520; 90574</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50398; 83590</t>
+          <t>51207; 83935</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32694; 64580</t>
+          <t>44071; 74386</t>
         </is>
       </c>
     </row>
